--- a/stories/arbres/ATOM-TMP.SAI.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nora est dans le jardin avec papa. Maman ouvre la porte. Un grand cerisier est là. Papa dit : il y a quatre saisons. Au printemps, Nora voit des fleurs. Les fleurs sentent bon. En été, il fait chaud. Nora boit de l'eau. En automne, les feuilles tombent. Elles sont rouges. En hiver, Nora met son manteau. Papa dit un signe chacune. Fleurs, chaud, feuilles, manteau. Nora répète : quatre saisons. Un signe chacune. Parce qu'elle nomme, elle comprend le temps. Maman dit : merci Nora. Nora touche une feuille sèche.</t>
+          <t>Nora est dans le jardin avec papa. Maman ouvre la porte. Un grand cerisier est là. Il y a quatre saisons. Au printemps, Nora voit des fleurs. Les fleurs sentent bon. En été, il fait chaud. Nora boit de l'eau. En automne, les feuilles tombent. Elles sont rouges. En hiver, Nora met son manteau. Papa dit un signe chacune. Fleurs, chaud, feuilles, manteau. Nora répète : quatre saisons. Un signe chacune. Parce qu'elle nomme, elle comprend le temps. Merci Nora. Nora touche une feuille sèche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nora est dans le jardin avec papa. Maman ouvre la porte. Un grand cerisier est là.
+papa|Il y a quatre saisons. Au printemps, Nora voit des fleurs.
+narrateur|Les fleurs sentent bon. En été, il fait chaud. Nora boit de l'eau. En automne, les feuilles tombent. Elles sont rouges. En hiver, Nora met son manteau. Papa dit un signe chacune. Fleurs, chaud, feuilles, manteau. Nora répète : quatre saisons. Un signe chacune. Parce qu'elle nomme, elle comprend le temps.
+maman|Merci Nora.
+narrateur|Nora touche une feuille sèche.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Nora met son manteau. Quelle saison est-ce ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a nommé les quatre saisons. Un signe chacune. Papa et maman l'ont aidée.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Nora ramasse une feuille. Papa tient sa main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SAI.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Nora touche une feuille sèche.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Nora met son manteau. Quelle saison est-ce ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Nora a nommé les quatre saisons. Un signe chacune. Papa et maman l'ont aidée.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1847,7 @@
           <t>narrateur|Nora ramasse une feuille. Papa tient sa main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SAI.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les saisons de Nora</t>
+          <t>La tomate de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila veut voir la tomate du jardin. Au printemps le bourgeon est collé. Plus tard l'été chauffe, la tomate rougit. Elle la cueille.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nora est dans le jardin avec papa. Maman ouvre la porte. Un grand cerisier est là. Il y a quatre saisons. Au printemps, Nora voit des fleurs. Les fleurs sentent bon. En été, il fait chaud. Nora boit de l'eau. En automne, les feuilles tombent. Elles sont rouges. En hiver, Nora met son manteau. Papa dit un signe chacune. Fleurs, chaud, feuilles, manteau. Nora répète : quatre saisons. Un signe chacune. Parce qu'elle nomme, elle comprend le temps. Merci Nora. Nora touche une feuille sèche.</t>
+          <t>Le cerisier du jardin a un bourgeon collé. La terre sent l'eau douce. Un arrosoir bleu penche près du mur. Maman ouvre le petit portail. Ça claque, tout léger. Viens voir le pied, Mila. En ce moment, Mila s'accroupit. Un bourgeon vert brille sur la tige. Il est fermé. Il s'ouvre, plus tard. C'est le printemps, tout petit. Mila touche le bourgeon, un doigt. Il est frais, un peu collant. Je veux une tomate. Pas encore. Il faut le soleil des jours chauds. Ils arrosent un peu, pas trop. L'eau fait un rond sombre. Un oiseau boit dans la soucoupe. Pousse, petit. On reviendra. Plus tard, le jardin est chaud. Les dalles brûlent un peu les pieds. Ça sent la feuille chaude, et la terre. Le pied de tomate a grandi. Des feuilles piquent, tout doux. Une tomate ! Elle est encore pâle. On attend le rouge. Mila revient le lendemain. Une tomate a un flanc rose. Presque. Encore un peu de chaud. Le soleil tape le mur du fond. Une abeille tourne, puis part. Mila attend, les mains sur les genoux. Un jour, la tomate est rouge. Elle est chaude au toucher. Je la cueille ? Oui. Tout doucement, près de la tige. Mila tourne, puis tire. La tomate reste dans sa paume. Elle est lourde. C'est l'été, dans le jardin. Tu t'en souviens, du bourgeon ? Il était fermé. Maintenant elle est rouge.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nora est dans le jardin avec papa. Maman ouvre la porte. Un grand cerisier est là. Papa dit : il y a &lt;emphasis level="moderate"&gt;quatre&lt;/emphasis&gt; saisons. Au printemps, Nora voit des fleurs. Les fleurs sentent bon. En été, il fait chaud. Nora boit de l'eau. En automne, les feuilles tombent. Elles sont rouges. En hiver, Nora met son manteau. Papa dit un signe chacune. Fleurs, chaud, feuilles, manteau. Nora répète : quatre saisons. Un signe chacune. Parce qu'elle nomme, elle comprend le temps. Maman dit : merci Nora. Nora touche une feuille sèche.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le cerisier du jardin a un bourgeon collé. La terre sent l'eau douce. Un arrosoir bleu penche près du mur. Maman ouvre le petit portail. Ça claque, tout léger. Viens voir le pied, Mila. En ce moment, Mila s'accroupit. Un bourgeon vert brille sur la tige. Il est fermé. Il s'ouvre, plus tard. C'est le printemps, tout petit. Mila touche le bourgeon, un doigt. Il est frais, un peu collant. Je veux une tomate. Pas encore. Il faut le soleil des jours chauds. Ils arrosent un peu, pas trop. L'eau fait un rond sombre. Un oiseau boit dans la soucoupe. Pousse, petit. On reviendra. Plus tard, le jardin est chaud. Les dalles brûlent un peu les pieds. Ça sent la feuille chaude, et la terre. Le pied de tomate a grandi. Des feuilles piquent, tout doux. Une tomate ! Elle est encore pâle. On attend le rouge. Mila revient le lendemain. Une tomate a un flanc rose. Presque. Encore un peu de chaud. Le soleil tape le mur du fond. Une abeille tourne, puis part. Mila attend, les mains sur les genoux. Un jour, la tomate est rouge. Elle est chaude au toucher. Je la cueille ? Oui. Tout doucement, près de la tige. Mila tourne, puis tire. La tomate reste dans sa paume. Elle est lourde. C'est l'été, dans le jardin. Tu t'en souviens, du bourgeon ? Il était fermé. Maintenant elle est rouge.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,11 +1324,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Nora est dans le jardin avec papa. Maman ouvre la porte. Un grand cerisier est là.
-papa|Il y a quatre saisons. Au printemps, Nora voit des fleurs.
-narrateur|Les fleurs sentent bon. En été, il fait chaud. Nora boit de l'eau. En automne, les feuilles tombent. Elles sont rouges. En hiver, Nora met son manteau. Papa dit un signe chacune. Fleurs, chaud, feuilles, manteau. Nora répète : quatre saisons. Un signe chacune. Parce qu'elle nomme, elle comprend le temps.
-maman|Merci Nora.
-narrateur|Nora touche une feuille sèche.</t>
+          <t>narrateur|Le cerisier du jardin a un bourgeon collé.
+narrateur|La terre sent l'eau douce.
+narrateur|Un arrosoir bleu penche près du mur.
+narrateur|Maman ouvre le petit portail.
+narrateur|Ça claque, tout léger.
+papa|Viens voir le pied, Mila.
+narrateur|En ce moment, Mila s'accroupit.
+narrateur|Un bourgeon vert brille sur la tige.
+enfant-f|Il est fermé.
+maman|Il s'ouvre, plus tard.
+papa|C'est le printemps, tout petit.
+narrateur|Mila touche le bourgeon, un doigt.
+narrateur|Il est frais, un peu collant.
+enfant-f|Je veux une tomate.
+maman|Pas encore.
+maman|Il faut le soleil des jours chauds.
+narrateur|Ils arrosent un peu, pas trop.
+narrateur|L'eau fait un rond sombre.
+narrateur|Un oiseau boit dans la soucoupe.
+enfant-f|Pousse, petit.
+papa|On reviendra.
+narrateur|Plus tard, le jardin est chaud.
+narrateur|Les dalles brûlent un peu les pieds.
+narrateur|Ça sent la feuille chaude, et la terre.
+narrateur|Le pied de tomate a grandi.
+narrateur|Des feuilles piquent, tout doux.
+enfant-f|Une tomate !
+maman|Elle est encore pâle.
+papa|On attend le rouge.
+narrateur|Mila revient le lendemain.
+narrateur|Une tomate a un flanc rose.
+enfant-f|Presque.
+maman|Encore un peu de chaud.
+narrateur|Le soleil tape le mur du fond.
+narrateur|Une abeille tourne, puis part.
+narrateur|Mila attend, les mains sur les genoux.
+narrateur|Un jour, la tomate est rouge.
+narrateur|Elle est chaude au toucher.
+enfant-f|Je la cueille ?
+papa|Oui.
+papa|Tout doucement, près de la tige.
+narrateur|Mila tourne, puis tire.
+narrateur|La tomate reste dans sa paume.
+enfant-f|Elle est lourde.
+maman|C'est l'été, dans le jardin.
+papa|Tu t'en souviens, du bourgeon ?
+enfant-f|Il était fermé.
+enfant-f|Maintenant elle est rouge.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,12 +1403,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nora met son manteau. Quelle saison est-ce ?</t>
+          <t>La tomate est rouge et chaude. Quelle saison est-ce ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nora met son manteau. Quelle saison est-ce ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La tomate est rouge et chaude. Quelle saison est-ce ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,12 +1418,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>hiver</t>
+          <t>été</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>hiver | l'hiver | en hiver</t>
+          <t>été | l'été | en été | tomate | chaud</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1438,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>En hiver, on met le manteau. Quelle saison ?</t>
+          <t>La tomate est rouge. Quelle saison ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1432,7 +1487,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1559,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Nora met son manteau. Quelle saison est-ce ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La tomate est rouge et chaude.
+narrateur|Quelle saison est-ce ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nora a nommé les quatre saisons. Un signe chacune. Papa et maman l'ont aidée.</t>
+          <t>Maman rince la tomate sous le robinet. L'eau fait une perle sur la peau. Je goûte ? Un morceau chacun. Papa coupe, tout net. Le dedans est rose, avec des pépins. C'est doux, et un peu chaud. Merci, Mila. Tu as attendu le rouge. Un pépin reste sur l'assiette. Mila le pousse du doigt.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nora a nommé les &lt;emphasis level="moderate"&gt;quatre&lt;/emphasis&gt; saisons. Un signe chacune. Papa et maman l'ont aidée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman rince la tomate sous le robinet. L'eau fait une perle sur la peau. Je goûte ? Un morceau chacun. Papa coupe, tout net. Le dedans est rose, avec des pépins. C'est doux, et un peu chaud. Merci, Mila. Tu as attendu le rouge. Un pépin reste sur l'assiette. Mila le pousse du doigt.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1600,7 +1655,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1676,10 +1731,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nora a nommé les quatre saisons. Un signe chacune. Papa et maman l'ont aidée.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Maman rince la tomate sous le robinet.
+narrateur|L'eau fait une perle sur la peau.
+enfant-f|Je goûte ?
+papa|Un morceau chacun.
+narrateur|Papa coupe, tout net.
+narrateur|Le dedans est rose, avec des pépins.
+enfant-f|C'est doux, et un peu chaud.
+maman|Merci, Mila.
+maman|Tu as attendu le rouge.
+narrateur|Un pépin reste sur l'assiette.
+narrateur|Mila le pousse du doigt.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,12 +1768,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nora ramasse une feuille. Papa tient sa main.</t>
+          <t>Ils reviennent près du pied. La tige a un petit chapeau vide. Il reste des vertes. Elles rougiront aussi. Le jardin a le temps. L'arrosoir bleu fait une ombre ronde. Mila sent encore la tomate aux doigts.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nora ramasse &lt;emphasis level="moderate"&gt;un&lt;/emphasis&gt;e feuille. Papa tient sa main.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils reviennent près du pied. La tige a un petit chapeau vide. Il reste des vertes. Elles rougiront aussi. Le jardin a le temps. L'arrosoir bleu fait une ombre ronde. Mila sent encore la tomate aux doigts.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1772,7 +1836,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1844,10 +1908,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nora ramasse une feuille. Papa tient sa main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils reviennent près du pied.
+narrateur|La tige a un petit chapeau vide.
+enfant-f|Il reste des vertes.
+papa|Elles rougiront aussi.
+maman|Le jardin a le temps.
+narrateur|L'arrosoir bleu fait une ombre ronde.
+narrateur|Mila sent encore la tomate aux doigts.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,12 +1941,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le mur du fond garde la chaleur. Une abeille revient, puis s'en va. Le bourgeon a bien poussé. Oui. La tige vide bouge un peu, dans l'air. Mila referme le petit portail.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le mur du fond garde la chaleur. Une abeille revient, puis s'en va. Le bourgeon a bien poussé. Oui. La tige vide bouge un peu, dans l'air. Mila referme le petit portail.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1933,14 +2002,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2012,10 +2081,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le mur du fond garde la chaleur.
+narrateur|Une abeille revient, puis s'en va.
+enfant-f|Le bourgeon a bien poussé.
+papa|Oui.
+narrateur|La tige vide bouge un peu, dans l'air.
+narrateur|Mila referme le petit portail.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2145,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SAI.001-02.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin, pied de tomate, deux moments de l'année</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nora, papa, maman</t>
+          <t>Mila, papa, maman</t>
         </is>
       </c>
     </row>
